--- a/docs/hotelngo/HotelNGo_페이지별_구현현황_및_구성도.xlsx
+++ b/docs/hotelngo/HotelNGo_페이지별_구현현황_및_구성도.xlsx
@@ -2,16 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" r:id="Rae3093eba1fd4a9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체화면목록(191)" sheetId="2" r:id="Rd42de5cb22cf4b35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용자흐름(47)" sheetId="3" r:id="R2e43988cdde04099"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메뉴구조도" sheetId="4" r:id="R8e84cd5310eb45d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="목표화면매트릭스" sheetId="5" r:id="R8222d4e7ec3440ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="팝업·레이어" sheetId="6" r:id="R969e7fe7d0d54095"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="원문요구대조" sheetId="7" r:id="Rfc9d952e0e86428d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="미구현백로그" sheetId="8" r:id="R1c6b1f615813434e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="프로세스유스케이스" sheetId="9" r:id="R14e94ae757364cab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검증결과" sheetId="10" r:id="R2becabb8bff74b6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" r:id="Ra665dd90def846d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체화면목록(191)" sheetId="2" r:id="R32f772ce57ac4deb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용자흐름(47)" sheetId="3" r:id="R845caa42623145e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메뉴구조도" sheetId="4" r:id="R87ac50f0fb834770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="목표화면매트릭스" sheetId="5" r:id="R1ecdf7135b75463d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="팝업·레이어" sheetId="6" r:id="R31e7fffde54c4835"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="원문요구대조" sheetId="7" r:id="R0a56dce84a7f4193"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="미구현백로그" sheetId="8" r:id="Rfeec41df096e4f1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="프로세스유스케이스" sheetId="9" r:id="Rb527fc0ddb4441c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검증결과" sheetId="10" r:id="R2234b94fd1e94f7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메뉴정체성·여행조합" sheetId="11" r:id="Rd82a1f3661b54d0a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,7 +27,7 @@
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="30">
+  <x:fonts count="41">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -191,8 +192,69 @@
       <x:color rgb="FF2F6BFF"/>
       <x:name val="맑은 고딕"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="맑은 고딕"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="20"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF24436B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13"/>
+      <x:color rgb="FF101828"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="20"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="맑은 고딕"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF24436B"/>
+      <x:name val="맑은 고딕"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="맑은 고딕"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13"/>
+      <x:color rgb="FF101828"/>
+      <x:name val="맑은 고딕"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF24436B"/>
+      <x:name val="맑은 고딕"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF101828"/>
+      <x:name val="맑은 고딕"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -239,8 +301,38 @@
         <x:fgColor rgb="FFE6FFFB"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF101828"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F0FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF14295F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9F2FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF7EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0F0"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="7">
+  <x:borders count="19">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -290,11 +382,116 @@
         <x:color rgb="FF172554"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD7DEE8"/>
+      </x:right>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="139">
+  <x:cellXfs count="250">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -640,18 +837,305 @@
     <x:xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="201" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="31" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="32" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="32" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="33" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="33" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="34" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="34" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="39" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="15" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="40" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="13" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="15" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="72">
+  <x:dxfs count="73">
     <x:dxf>
       <x:font>
         <x:b/>
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF8EE"/>
         </x:patternFill>
       </x:fill>
@@ -662,7 +1146,7 @@
         <x:color rgb="FF2F6BFF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF0FF"/>
         </x:patternFill>
       </x:fill>
@@ -673,7 +1157,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -684,7 +1168,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -695,7 +1179,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -706,7 +1190,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -717,7 +1201,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF8EE"/>
         </x:patternFill>
       </x:fill>
@@ -728,7 +1212,7 @@
         <x:color rgb="FF2F6BFF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF0FF"/>
         </x:patternFill>
       </x:fill>
@@ -739,7 +1223,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -750,7 +1234,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -761,7 +1245,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -772,7 +1256,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -783,7 +1267,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF8EE"/>
         </x:patternFill>
       </x:fill>
@@ -794,7 +1278,7 @@
         <x:color rgb="FF2F6BFF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF0FF"/>
         </x:patternFill>
       </x:fill>
@@ -805,7 +1289,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -816,7 +1300,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -827,7 +1311,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -838,7 +1322,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -849,7 +1333,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF8EE"/>
         </x:patternFill>
       </x:fill>
@@ -860,7 +1344,7 @@
         <x:color rgb="FF2F6BFF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF0FF"/>
         </x:patternFill>
       </x:fill>
@@ -871,7 +1355,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -882,7 +1366,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -893,7 +1377,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -904,7 +1388,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -915,7 +1399,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF8EE"/>
         </x:patternFill>
       </x:fill>
@@ -926,7 +1410,7 @@
         <x:color rgb="FF2F6BFF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF0FF"/>
         </x:patternFill>
       </x:fill>
@@ -937,7 +1421,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -948,7 +1432,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -959,7 +1443,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -970,7 +1454,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -981,7 +1465,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -992,7 +1476,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -1003,7 +1487,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF8EE"/>
         </x:patternFill>
       </x:fill>
@@ -1014,7 +1498,7 @@
         <x:color rgb="FF2F6BFF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF0FF"/>
         </x:patternFill>
       </x:fill>
@@ -1025,7 +1509,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -1036,7 +1520,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1047,7 +1531,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1058,7 +1542,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -1069,7 +1553,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF8EE"/>
         </x:patternFill>
       </x:fill>
@@ -1080,7 +1564,7 @@
         <x:color rgb="FF2F6BFF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF0FF"/>
         </x:patternFill>
       </x:fill>
@@ -1091,7 +1575,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -1102,7 +1586,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1113,7 +1597,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1124,7 +1608,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -1135,7 +1619,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF8EE"/>
         </x:patternFill>
       </x:fill>
@@ -1146,7 +1630,7 @@
         <x:color rgb="FF2F6BFF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF0FF"/>
         </x:patternFill>
       </x:fill>
@@ -1157,7 +1641,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -1168,7 +1652,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1179,7 +1663,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1190,7 +1674,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -1201,7 +1685,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1212,7 +1696,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -1223,7 +1707,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF8EE"/>
         </x:patternFill>
       </x:fill>
@@ -1234,7 +1718,7 @@
         <x:color rgb="FF2F6BFF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF0FF"/>
         </x:patternFill>
       </x:fill>
@@ -1245,7 +1729,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -1256,7 +1740,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1267,7 +1751,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1278,7 +1762,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -1289,7 +1773,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1300,7 +1784,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -1311,7 +1795,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF8EE"/>
         </x:patternFill>
       </x:fill>
@@ -1322,7 +1806,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1333,7 +1817,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF8EE"/>
         </x:patternFill>
       </x:fill>
@@ -1344,7 +1828,7 @@
         <x:color rgb="FF2F6BFF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF0FF"/>
         </x:patternFill>
       </x:fill>
@@ -1355,7 +1839,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -1366,7 +1850,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1377,7 +1861,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1388,7 +1872,7 @@
         <x:color rgb="FF9A6700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF7E0"/>
         </x:patternFill>
       </x:fill>
@@ -1399,7 +1883,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF8EE"/>
         </x:patternFill>
       </x:fill>
@@ -1410,7 +1894,7 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEECEC"/>
         </x:patternFill>
       </x:fill>
@@ -1421,7 +1905,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF8EE"/>
         </x:patternFill>
       </x:fill>
@@ -1432,8 +1916,15 @@
         <x:color rgb="FFDC2626"/>
       </x:font>
       <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFEECEC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
         <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEECEC"/>
+          <x:bgColor rgb="FFEAF7EF"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -1442,7 +1933,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PageStatusTable" displayName="PageStatusTable" ref="A5:S196" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PageStatusTable" displayName="PageStatusTable" ref="A5:S198" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="No"/>
     <x:tableColumn id="2" name="Realm"/>
@@ -1468,8 +1959,59 @@
 </x:table>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="MenuIdentityTable" displayName="MenuIdentityTable" ref="A4:I10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="9">
+    <x:tableColumn id="1" name="상단 메뉴"/>
+    <x:tableColumn id="2" name="고객 질문"/>
+    <x:tableColumn id="3" name="메뉴의 책임"/>
+    <x:tableColumn id="4" name="필수 입력"/>
+    <x:tableColumn id="5" name="주요 출력"/>
+    <x:tableColumn id="6" name="핵심 행동"/>
+    <x:tableColumn id="7" name="대표 화면"/>
+    <x:tableColumn id="8" name="현재 판정"/>
+    <x:tableColumn id="9" name="실서비스 Gap"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="TripJourneyTable" displayName="TripJourneyTable" ref="A13:I20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="9">
+    <x:tableColumn id="1" name="단계"/>
+    <x:tableColumn id="2" name="출발 화면"/>
+    <x:tableColumn id="3" name="고객 행동"/>
+    <x:tableColumn id="4" name="다음 화면"/>
+    <x:tableColumn id="5" name="유지할 컨텍스트"/>
+    <x:tableColumn id="6" name="검증 결과"/>
+    <x:tableColumn id="7" name="현재 구현"/>
+    <x:tableColumn id="8" name="남은 Gap"/>
+    <x:tableColumn id="9" name="인수 조건"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="ServiceBoundaryTable" displayName="ServiceBoundaryTable" ref="A23:I27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="9">
+    <x:tableColumn id="1" name="구분"/>
+    <x:tableColumn id="2" name="현재 동작"/>
+    <x:tableColumn id="3" name="데이터"/>
+    <x:tableColumn id="4" name="사용자에게 표시"/>
+    <x:tableColumn id="5" name="실제 서비스 전환"/>
+    <x:tableColumn id="6" name="우선순위"/>
+    <x:tableColumn id="7" name="대표 문서"/>
+    <x:tableColumn id="8" name="검증"/>
+    <x:tableColumn id="9" name="비고"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PageFlowTable" displayName="PageFlowTable" ref="A5:M52" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PageFlowTable" displayName="PageFlowTable" ref="A5:M59" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="Flow ID"/>
     <x:tableColumn id="2" name="Realm"/>
@@ -1490,7 +2032,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="MenuArchitectureTable" displayName="MenuArchitectureTable" ref="A5:L96" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="MenuArchitectureTable" displayName="MenuArchitectureTable" ref="A5:L97" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Realm"/>
     <x:tableColumn id="2" name="서비스 영역"/>
@@ -1510,7 +2052,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TargetScreenMatrixTable" displayName="TargetScreenMatrixTable" ref="A5:O196" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TargetScreenMatrixTable" displayName="TargetScreenMatrixTable" ref="A5:O198" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="15">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Realm"/>
@@ -1595,7 +2137,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="UseCaseTable" displayName="UseCaseTable" ref="A5:L23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="UseCaseTable" displayName="UseCaseTable" ref="A5:L24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="역할"/>
@@ -1615,7 +2157,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="CriticalFlowTable" displayName="CriticalFlowTable" ref="A16:H30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="CriticalFlowTable" displayName="CriticalFlowTable" ref="A16:H33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Flow ID"/>
     <x:tableColumn id="2" name="핵심 흐름"/>
@@ -1857,7 +2399,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="72" t="str">
-        <x:v>현재 191개 HTML, 47개 사용자 흐름, 전체 메뉴 구조와 실제 서비스 백로그를 서로 다른 기준으로 분리한 실행용 보고서</x:v>
+        <x:v>현재 193개 HTML, 54개 사용자 흐름, 92개 메뉴 노드와 실제 서비스 백로그를 서로 다른 기준으로 분리한 실행용 보고서</x:v>
       </x:c>
       <x:c r="B2" s="72"/>
       <x:c r="C2" s="72"/>
@@ -1887,7 +2429,7 @@
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="74" t="str">
-        <x:v>중요: 191은 현재 존재하는 제품 HTML 파일 수이고 47은 사용자 흐름 단계 수입니다. 계획 기준선의 화면은 모두 생성됐지만 실제 서버·DB·결제·PMS 쓰기·AI/RAG 완료를 의미하지는 않습니다.</x:v>
+        <x:v>중요: 193은 현재 존재하는 제품 HTML 파일 수이고 54는 사용자 흐름 단계 수입니다. 화면·Mock 구현은 실제 서버·DB·결제·PMS 쓰기·AI/RAG 완료를 의미하지 않습니다.</x:v>
       </x:c>
       <x:c r="B4" s="74"/>
       <x:c r="C4" s="74"/>
@@ -1942,8 +2484,8 @@
         <x:v>현재 HTML 화면</x:v>
       </x:c>
       <x:c r="B7" s="79" t="n">
-        <x:f>COUNTA('전체화면목록(191)'!$A$6:$A$196)</x:f>
-        <x:v>191</x:v>
+        <x:f>COUNTA('전체화면목록(191)'!$E$6:$E$198)</x:f>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C7" s="73"/>
       <x:c r="D7" s="80" t="str">
@@ -1969,8 +2511,8 @@
         <x:v>현재 화면 행</x:v>
       </x:c>
       <x:c r="B8" s="83" t="n">
-        <x:f>COUNTA('전체화면목록(191)'!$A$6:$A$196)</x:f>
-        <x:v>191</x:v>
+        <x:f>COUNTA('전체화면목록(191)'!$E$6:$E$198)</x:f>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C8" s="73"/>
       <x:c r="D8" s="80" t="str">
@@ -1996,8 +2538,8 @@
         <x:v>사용자 흐름 단계</x:v>
       </x:c>
       <x:c r="B9" s="83" t="n">
-        <x:f>COUNTA('사용자흐름(47)'!$A$6:$A$52)</x:f>
-        <x:v>47</x:v>
+        <x:f>COUNTA('사용자흐름(47)'!$A$6:$A$59)</x:f>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C9" s="73"/>
       <x:c r="D9" s="80" t="str">
@@ -2023,12 +2565,11 @@
         <x:v>메뉴 노드</x:v>
       </x:c>
       <x:c r="B10" s="83" t="n">
-        <x:f>COUNTA('메뉴구조도'!$A$6:$A$96)</x:f>
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C10" s="73"/>
       <x:c r="D10" s="80" t="str">
-        <x:v>• 191개 화면 데스크톱/모바일 UI 회귀와 공통 Drawer/Dialog/Toast</x:v>
+        <x:v>• 193개 화면 데스크톱/모바일 UI 회귀와 공통 Drawer/Dialog/Toast</x:v>
       </x:c>
       <x:c r="E10" s="80"/>
       <x:c r="F10" s="80"/>
@@ -2077,8 +2618,8 @@
         <x:v>목표 화면 기준선</x:v>
       </x:c>
       <x:c r="B12" s="83" t="n">
-        <x:f>COUNTA('목표화면매트릭스'!$A$6:$A$196)</x:f>
-        <x:v>191</x:v>
+        <x:f>COUNTA('목표화면매트릭스'!$E$6:$E$198)</x:f>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C12" s="73"/>
       <x:c r="D12" s="73"/>
@@ -2102,8 +2643,7 @@
         <x:v>Mock 동작 화면</x:v>
       </x:c>
       <x:c r="B13" s="83" t="n">
-        <x:f>COUNTIF('전체화면목록(191)'!$I$6:$I$196,"Mock 동작")</x:f>
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C13" s="73"/>
       <x:c r="D13" s="75" t="str">
@@ -2115,13 +2655,13 @@
       <x:c r="H13" s="76"/>
       <x:c r="I13" s="73"/>
       <x:c r="J13" s="85" t="str">
-        <x:v>검토 기준일</x:v>
-      </x:c>
-      <x:c r="K13" s="86" t="n">
-        <x:v>46226</x:v>
-      </x:c>
-      <x:c r="L13" s="86" t="n">
-        <x:v>46226</x:v>
+        <x:v>메뉴·여행 조합 기준</x:v>
+      </x:c>
+      <x:c r="K13" s="86" t="str">
+        <x:v>docs/hotelngo/24-product-menu-identity-and-trip-composer-blueprint.md</x:v>
+      </x:c>
+      <x:c r="L13" s="86" t="str">
+        <x:v>https://github.com/giry02/hotelngo/blob/main/docs/hotelngo/24-product-menu-identity-and-trip-composer-blueprint.md</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="29" customHeight="1">
@@ -2141,9 +2681,15 @@
       <x:c r="G14" s="89"/>
       <x:c r="H14" s="89"/>
       <x:c r="I14" s="73"/>
-      <x:c r="J14" s="73"/>
-      <x:c r="K14" s="73"/>
-      <x:c r="L14" s="73"/>
+      <x:c r="J14" s="140" t="str">
+        <x:v>검토 기준일</x:v>
+      </x:c>
+      <x:c r="K14" s="141" t="n">
+        <x:v>46227</x:v>
+      </x:c>
+      <x:c r="L14" s="141" t="n">
+        <x:v>46227</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="29" customHeight="1">
       <x:c r="A15" s="73"/>
@@ -2214,7 +2760,7 @@
       <x:c r="B19" s="73"/>
       <x:c r="C19" s="73"/>
       <x:c r="D19" s="89" t="str">
-        <x:v>6. 일정 드래그·시간/이동 충돌 검증·공유/협업</x:v>
+        <x:v>6. 일정 드래그·실시간 이동거리·공동 편집 (시간 충돌·필수 항목 검증은 Mock 구현)</x:v>
       </x:c>
       <x:c r="E19" s="89"/>
       <x:c r="F19" s="89"/>
@@ -2453,10 +2999,10 @@
         <x:v>제품 HTML 도달성</x:v>
       </x:c>
       <x:c r="B5" s="136" t="n">
-        <x:v>191</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C5" s="81" t="str">
-        <x:v>191개 중 통과</x:v>
+        <x:v>193개 총괄</x:v>
       </x:c>
       <x:c r="D5" s="109" t="str">
         <x:v>PASS</x:v>
@@ -2471,10 +3017,10 @@
         <x:v>내부 HTML 링크</x:v>
       </x:c>
       <x:c r="B6" s="137" t="n">
-        <x:v>515</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="C6" s="84" t="str">
-        <x:v>정적 링크 검사</x:v>
+        <x:v>정적 내부 HTML 링크 검사</x:v>
       </x:c>
       <x:c r="D6" s="111" t="str">
         <x:v>PASS</x:v>
@@ -2543,7 +3089,7 @@
         <x:v>버튼</x:v>
       </x:c>
       <x:c r="B10" s="137" t="n">
-        <x:v>185</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C10" s="84" t="str">
         <x:v>정적 분류 대상</x:v>
@@ -2579,7 +3125,7 @@
         <x:v>업무 유스케이스</x:v>
       </x:c>
       <x:c r="B12" s="137" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="84" t="str">
         <x:v>역할별 프로세스</x:v>
@@ -2597,7 +3143,7 @@
         <x:v>로컬 Mock 통과</x:v>
       </x:c>
       <x:c r="B13" s="137" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C13" s="84" t="str">
         <x:v>JSON 상태 기반</x:v>
@@ -2999,6 +3545,84 @@
         <x:v>https://github.com/giry02/hotelngo/blob/main/docs/hotelngo/22-end-to-end-process-validation.md</x:v>
       </x:c>
       <x:c r="H30" s="85" t="str"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>FLOW-DISCOVERY-CONTEXT</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>목적지 선택 전/후 여행 발견</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>목적지 미정 설명 → 다낭 선택 → 다낭 히어로·일정/호텔/즐길거리 CTA</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>로컬 JSON Mock</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>http://127.0.0.1:8791/discover.html?destination=다낭</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>docs/hotelngo/24-product-menu-identity-and-trip-composer-blueprint.md</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>다른 도시 콘텐츠는 참고용으로 명시</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>FLOW-MULTIDAY</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>4박 5일 다카테고리 일정 편집</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>5개 DAY·14개 항목·7개 카테고리·DAY 3 스파 추가·시간 충돌 0·저장 Toast</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>로컬 JSON Mock</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>http://127.0.0.1:8791/trip-planner.html?destination=다낭&amp;nights=4</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>docs/hotelngo/24-product-menu-identity-and-trip-composer-blueprint.md</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>실시간 가격·재고·지도 이동시간 미연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>FLOW-AI-MULTICATEGORY</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>AI 조건에서 동일 TripDraft 생성</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>다낭 4박5일·호텔·픽업·맛집·18홀·스파·호이안 요청 → 5일 14개 항목 편집기</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>규칙형 JSON Mock</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>http://127.0.0.1:8791/ai-travel.html</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>docs/hotelngo/16-ai-travel-implementation-report.md</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>실 LLM/RAG 미연결</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3021,7 +3645,708 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f596a48ec844d64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf459d568e1214cbd"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="35" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="32" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="31" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="21" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="31" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="192" t="str">
+        <x:v>HotelNGo 메뉴 정체성과 4박 5일 여행 조합 기준</x:v>
+      </x:c>
+      <x:c r="B1" s="192"/>
+      <x:c r="C1" s="192"/>
+      <x:c r="D1" s="192"/>
+      <x:c r="E1" s="192"/>
+      <x:c r="F1" s="192"/>
+      <x:c r="G1" s="192"/>
+      <x:c r="H1" s="192"/>
+      <x:c r="I1" s="192"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="215" t="str">
+        <x:v>목적지 발견부터 숙소·랜드마크·식사·골프·스파·이동을 날짜별로 조합하고 예약 준비까지 이어지는 고객 기준선</x:v>
+      </x:c>
+      <x:c r="B2" s="215"/>
+      <x:c r="C2" s="215"/>
+      <x:c r="D2" s="215"/>
+      <x:c r="E2" s="215"/>
+      <x:c r="F2" s="215"/>
+      <x:c r="G2" s="215"/>
+      <x:c r="H2" s="215"/>
+      <x:c r="I2" s="215"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="140"/>
+      <x:c r="B3" s="140"/>
+      <x:c r="C3" s="140"/>
+      <x:c r="D3" s="140"/>
+      <x:c r="E3" s="140"/>
+      <x:c r="F3" s="140"/>
+      <x:c r="G3" s="140"/>
+      <x:c r="H3" s="140"/>
+      <x:c r="I3" s="140"/>
+    </x:row>
+    <x:row r="4" ht="26" customHeight="1">
+      <x:c r="A4" s="236" t="str">
+        <x:v>상단 메뉴</x:v>
+      </x:c>
+      <x:c r="B4" s="237" t="str">
+        <x:v>고객 질문</x:v>
+      </x:c>
+      <x:c r="C4" s="237" t="str">
+        <x:v>메뉴의 책임</x:v>
+      </x:c>
+      <x:c r="D4" s="237" t="str">
+        <x:v>필수 입력</x:v>
+      </x:c>
+      <x:c r="E4" s="237" t="str">
+        <x:v>주요 출력</x:v>
+      </x:c>
+      <x:c r="F4" s="237" t="str">
+        <x:v>핵심 행동</x:v>
+      </x:c>
+      <x:c r="G4" s="237" t="str">
+        <x:v>대표 화면</x:v>
+      </x:c>
+      <x:c r="H4" s="237" t="str">
+        <x:v>현재 판정</x:v>
+      </x:c>
+      <x:c r="I4" s="238" t="str">
+        <x:v>실서비스 Gap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="54" customHeight="1">
+      <x:c r="A5" s="218" t="str">
+        <x:v>여행 발견</x:v>
+      </x:c>
+      <x:c r="B5" s="218" t="str">
+        <x:v>어디로 갈지 모르겠는데 가고 싶게 해줘</x:v>
+      </x:c>
+      <x:c r="C5" s="218" t="str">
+        <x:v>도시·장면·테마·공개 일정으로 목적지를 발견</x:v>
+      </x:c>
+      <x:c r="D5" s="218" t="str">
+        <x:v>목적지 미정 또는 도시·계절·동행</x:v>
+      </x:c>
+      <x:c r="E5" s="218" t="str">
+        <x:v>도시·스토리·랜드마크·공개 일정</x:v>
+      </x:c>
+      <x:c r="F5" s="218" t="str">
+        <x:v>도시 선택·저장·일정 복사</x:v>
+      </x:c>
+      <x:c r="G5" s="218" t="str">
+        <x:v>discover.html</x:v>
+      </x:c>
+      <x:c r="H5" s="219" t="str">
+        <x:v>목적지 전/후 컨텍스트 구현</x:v>
+      </x:c>
+      <x:c r="I5" s="218" t="str">
+        <x:v>도시별 CMS·개인화 추천</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="54" customHeight="1">
+      <x:c r="A6" s="222" t="str">
+        <x:v>여행 일정</x:v>
+      </x:c>
+      <x:c r="B6" s="222" t="str">
+        <x:v>매일 무엇을 할지 직접 짜고 싶다</x:v>
+      </x:c>
+      <x:c r="C6" s="222" t="str">
+        <x:v>모든 업종을 날짜·시간별로 조합하는 핵심 작업 공간</x:v>
+      </x:c>
+      <x:c r="D6" s="222" t="str">
+        <x:v>목적지·날짜·인원</x:v>
+      </x:c>
+      <x:c r="E6" s="222" t="str">
+        <x:v>DAY별 타임라인·비용·충돌·예약 준비도</x:v>
+      </x:c>
+      <x:c r="F6" s="222" t="str">
+        <x:v>추가·이동·교체·삭제·저장</x:v>
+      </x:c>
+      <x:c r="G6" s="222" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="H6" s="223" t="str">
+        <x:v>4박 5일·7개 카테고리 Mock 구현</x:v>
+      </x:c>
+      <x:c r="I6" s="222" t="str">
+        <x:v>서버 Trip DB·지도·실재고·협업</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="54" customHeight="1">
+      <x:c r="A7" s="222" t="str">
+        <x:v>호텔</x:v>
+      </x:c>
+      <x:c r="B7" s="222" t="str">
+        <x:v>이 여행 날짜와 위치에 맞는 숙소는?</x:v>
+      </x:c>
+      <x:c r="C7" s="222" t="str">
+        <x:v>객실·요금·재고·정책 비교</x:v>
+      </x:c>
+      <x:c r="D7" s="222" t="str">
+        <x:v>목적지·체크인/아웃·인원</x:v>
+      </x:c>
+      <x:c r="E7" s="222" t="str">
+        <x:v>호텔·객실·Offer·가용상태</x:v>
+      </x:c>
+      <x:c r="F7" s="222" t="str">
+        <x:v>상세·후기·일정/카트 추가</x:v>
+      </x:c>
+      <x:c r="G7" s="222" t="str">
+        <x:v>hotels.html</x:v>
+      </x:c>
+      <x:c r="H7" s="223" t="str">
+        <x:v>PMS 구조 독립 Fixture 조회</x:v>
+      </x:c>
+      <x:c r="I7" s="222" t="str">
+        <x:v>Hotel_PMS 채널 API·실예약</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="54" customHeight="1">
+      <x:c r="A8" s="222" t="str">
+        <x:v>즐길거리</x:v>
+      </x:c>
+      <x:c r="B8" s="222" t="str">
+        <x:v>선택한 도시에서 무엇을 먹고 경험할까?</x:v>
+      </x:c>
+      <x:c r="C8" s="222" t="str">
+        <x:v>랜드마크·식사·골프·스파·투어·이동 카탈로그</x:v>
+      </x:c>
+      <x:c r="D8" s="222" t="str">
+        <x:v>목적지, 선택 시 날짜</x:v>
+      </x:c>
+      <x:c r="E8" s="222" t="str">
+        <x:v>이미지·소요시간·가격·예약방식</x:v>
+      </x:c>
+      <x:c r="F8" s="222" t="str">
+        <x:v>날짜·시간 선택 후 일정 추가</x:v>
+      </x:c>
+      <x:c r="G8" s="222" t="str">
+        <x:v>experiences.html</x:v>
+      </x:c>
+      <x:c r="H8" s="223" t="str">
+        <x:v>목적지 게이트·필터·일정 연결 구현</x:v>
+      </x:c>
+      <x:c r="I8" s="222" t="str">
+        <x:v>업체 실재고·지도 거리·운영시간</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="54" customHeight="1">
+      <x:c r="A9" s="222" t="str">
+        <x:v>AI 여행</x:v>
+      </x:c>
+      <x:c r="B9" s="222" t="str">
+        <x:v>조건을 말하면 여행 전체를 만들어줘</x:v>
+      </x:c>
+      <x:c r="C9" s="222" t="str">
+        <x:v>수동 편집기와 같은 TripDraft 생성·수정</x:v>
+      </x:c>
+      <x:c r="D9" s="222" t="str">
+        <x:v>도시·기간·인원·예산·취향</x:v>
+      </x:c>
+      <x:c r="E9" s="222" t="str">
+        <x:v>다카테고리 일자별 초안</x:v>
+      </x:c>
+      <x:c r="F9" s="222" t="str">
+        <x:v>생성 후 동일 편집기에서 수정</x:v>
+      </x:c>
+      <x:c r="G9" s="222" t="str">
+        <x:v>ai-travel.html</x:v>
+      </x:c>
+      <x:c r="H9" s="223" t="str">
+        <x:v>규칙형 JSON에서 전체 편집기로 연결</x:v>
+      </x:c>
+      <x:c r="I9" s="222" t="str">
+        <x:v>LLM/RAG·도구 호출·평가</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="54" customHeight="1">
+      <x:c r="A10" s="226" t="str">
+        <x:v>내 여행</x:v>
+      </x:c>
+      <x:c r="B10" s="226" t="str">
+        <x:v>만든 여행과 예약을 다시 관리하고 싶다</x:v>
+      </x:c>
+      <x:c r="C10" s="226" t="str">
+        <x:v>회원 소유 초안·예약·지난 여행·공유 관리</x:v>
+      </x:c>
+      <x:c r="D10" s="226" t="str">
+        <x:v>로그인·tripId</x:v>
+      </x:c>
+      <x:c r="E10" s="226" t="str">
+        <x:v>여행 목록·상태·바우처·후기</x:v>
+      </x:c>
+      <x:c r="F10" s="226" t="str">
+        <x:v>이어서 편집·예약 준비·공유</x:v>
+      </x:c>
+      <x:c r="G10" s="226" t="str">
+        <x:v>trips.html</x:v>
+      </x:c>
+      <x:c r="H10" s="227" t="str">
+        <x:v>저장 목록·편집 진입 Mock</x:v>
+      </x:c>
+      <x:c r="I10" s="226" t="str">
+        <x:v>서버 소유권·동기화·알림</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="239"/>
+      <x:c r="B11" s="240"/>
+      <x:c r="C11" s="240"/>
+      <x:c r="D11" s="240"/>
+      <x:c r="E11" s="240"/>
+      <x:c r="F11" s="240"/>
+      <x:c r="G11" s="240"/>
+      <x:c r="H11" s="240"/>
+      <x:c r="I11" s="241"/>
+    </x:row>
+    <x:row r="12" ht="28" customHeight="1">
+      <x:c r="A12" s="242" t="str">
+        <x:v>고객 흐름: 다낭 4박 5일</x:v>
+      </x:c>
+      <x:c r="B12" s="243"/>
+      <x:c r="C12" s="243"/>
+      <x:c r="D12" s="243"/>
+      <x:c r="E12" s="243"/>
+      <x:c r="F12" s="243"/>
+      <x:c r="G12" s="243"/>
+      <x:c r="H12" s="243"/>
+      <x:c r="I12" s="244"/>
+    </x:row>
+    <x:row r="13" ht="26" customHeight="1">
+      <x:c r="A13" s="245" t="str">
+        <x:v>단계</x:v>
+      </x:c>
+      <x:c r="B13" s="246" t="str">
+        <x:v>출발 화면</x:v>
+      </x:c>
+      <x:c r="C13" s="246" t="str">
+        <x:v>고객 행동</x:v>
+      </x:c>
+      <x:c r="D13" s="246" t="str">
+        <x:v>다음 화면</x:v>
+      </x:c>
+      <x:c r="E13" s="246" t="str">
+        <x:v>유지할 컨텍스트</x:v>
+      </x:c>
+      <x:c r="F13" s="246" t="str">
+        <x:v>검증 결과</x:v>
+      </x:c>
+      <x:c r="G13" s="246" t="str">
+        <x:v>현재 구현</x:v>
+      </x:c>
+      <x:c r="H13" s="246" t="str">
+        <x:v>남은 Gap</x:v>
+      </x:c>
+      <x:c r="I13" s="247" t="str">
+        <x:v>인수 조건</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="52" customHeight="1">
+      <x:c r="A14" s="218" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B14" s="218" t="str">
+        <x:v>discover.html</x:v>
+      </x:c>
+      <x:c r="C14" s="218" t="str">
+        <x:v>다낭을 선택하거나 AI로 도시 추천</x:v>
+      </x:c>
+      <x:c r="D14" s="218" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="E14" s="218" t="str">
+        <x:v>destination</x:v>
+      </x:c>
+      <x:c r="F14" s="218" t="str">
+        <x:v>다낭 선택 시 히어로·CTA도 다낭으로 변경</x:v>
+      </x:c>
+      <x:c r="G14" s="218" t="str">
+        <x:v>구현</x:v>
+      </x:c>
+      <x:c r="H14" s="218" t="str">
+        <x:v>개인화 도시 랭킹</x:v>
+      </x:c>
+      <x:c r="I14" s="218" t="str">
+        <x:v>목적지 없이 상품을 섞지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="52" customHeight="1">
+      <x:c r="A15" s="222" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B15" s="222" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="C15" s="222" t="str">
+        <x:v>출귀국일·성인 2명·4박 5일 설정</x:v>
+      </x:c>
+      <x:c r="D15" s="222" t="str">
+        <x:v>동일 화면</x:v>
+      </x:c>
+      <x:c r="E15" s="222" t="str">
+        <x:v>destination/dates/travelers</x:v>
+      </x:c>
+      <x:c r="F15" s="222" t="str">
+        <x:v>5개 DAY 생성</x:v>
+      </x:c>
+      <x:c r="G15" s="222" t="str">
+        <x:v>구현</x:v>
+      </x:c>
+      <x:c r="H15" s="222" t="str">
+        <x:v>항공 일정 자동 반영</x:v>
+      </x:c>
+      <x:c r="I15" s="222" t="str">
+        <x:v>4박이면 정확히 5일</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="52" customHeight="1">
+      <x:c r="A16" s="222" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B16" s="222" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="C16" s="222" t="str">
+        <x:v>추천 초안 확인</x:v>
+      </x:c>
+      <x:c r="D16" s="222" t="str">
+        <x:v>동일 화면</x:v>
+      </x:c>
+      <x:c r="E16" s="222" t="str">
+        <x:v>tripId/items</x:v>
+      </x:c>
+      <x:c r="F16" s="222" t="str">
+        <x:v>숙소1·이동3·식사4·랜드마크3·골프1·스파1·투어1</x:v>
+      </x:c>
+      <x:c r="G16" s="222" t="str">
+        <x:v>구현</x:v>
+      </x:c>
+      <x:c r="H16" s="222" t="str">
+        <x:v>실시간 가능 여부</x:v>
+      </x:c>
+      <x:c r="I16" s="222" t="str">
+        <x:v>여러 업종이 한 여행에 존재</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="52" customHeight="1">
+      <x:c r="A17" s="222" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B17" s="222" t="str">
+        <x:v>experiences.html</x:v>
+      </x:c>
+      <x:c r="C17" s="222" t="str">
+        <x:v>다낭 골프·스파·맛집 후보 탐색</x:v>
+      </x:c>
+      <x:c r="D17" s="222" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="E17" s="222" t="str">
+        <x:v>destination/focus</x:v>
+      </x:c>
+      <x:c r="F17" s="222" t="str">
+        <x:v>다른 도시 상품 미노출·골프 2개 필터</x:v>
+      </x:c>
+      <x:c r="G17" s="222" t="str">
+        <x:v>구현</x:v>
+      </x:c>
+      <x:c r="H17" s="222" t="str">
+        <x:v>운영시간·거리 정렬</x:v>
+      </x:c>
+      <x:c r="I17" s="222" t="str">
+        <x:v>목적지 선택 후 추천</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="52" customHeight="1">
+      <x:c r="A18" s="222" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B18" s="222" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="C18" s="222" t="str">
+        <x:v>DAY 3 18:00에 스파 추가</x:v>
+      </x:c>
+      <x:c r="D18" s="222" t="str">
+        <x:v>동일 화면</x:v>
+      </x:c>
+      <x:c r="E18" s="222" t="str">
+        <x:v>selectedDay/time</x:v>
+      </x:c>
+      <x:c r="F18" s="222" t="str">
+        <x:v>DAY 3에 골프·식사·스파 3개 공존</x:v>
+      </x:c>
+      <x:c r="G18" s="222" t="str">
+        <x:v>구현</x:v>
+      </x:c>
+      <x:c r="H18" s="222" t="str">
+        <x:v>드래그·지도 이동시간</x:v>
+      </x:c>
+      <x:c r="I18" s="222" t="str">
+        <x:v>항목마다 일자·시간 선택</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="52" customHeight="1">
+      <x:c r="A19" s="222" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B19" s="222" t="str">
+        <x:v>ai-travel.html</x:v>
+      </x:c>
+      <x:c r="C19" s="222" t="str">
+        <x:v>자연어로 호텔·픽업·맛집·골프·스파·호이안 요청</x:v>
+      </x:c>
+      <x:c r="D19" s="222" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="E19" s="222" t="str">
+        <x:v>prompt/destination/nights</x:v>
+      </x:c>
+      <x:c r="F19" s="222" t="str">
+        <x:v>5일·14개 다카테고리 항목 생성</x:v>
+      </x:c>
+      <x:c r="G19" s="222" t="str">
+        <x:v>구현</x:v>
+      </x:c>
+      <x:c r="H19" s="222" t="str">
+        <x:v>실 LLM/RAG</x:v>
+      </x:c>
+      <x:c r="I19" s="222" t="str">
+        <x:v>AI와 수동 편집기가 동일</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="52" customHeight="1">
+      <x:c r="A20" s="226" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B20" s="226" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="C20" s="226" t="str">
+        <x:v>충돌·비용·예약방식 확인 후 저장</x:v>
+      </x:c>
+      <x:c r="D20" s="226" t="str">
+        <x:v>trips.html</x:v>
+      </x:c>
+      <x:c r="E20" s="226" t="str">
+        <x:v>TripDraft</x:v>
+      </x:c>
+      <x:c r="F20" s="226" t="str">
+        <x:v>시간 충돌 0·저장 Toast 확인</x:v>
+      </x:c>
+      <x:c r="G20" s="226" t="str">
+        <x:v>Mock 구현</x:v>
+      </x:c>
+      <x:c r="H20" s="226" t="str">
+        <x:v>서버 DB·예약 전 재검증</x:v>
+      </x:c>
+      <x:c r="I20" s="226" t="str">
+        <x:v>허위 확정 없이 상태 구분</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="239"/>
+      <x:c r="B21" s="240"/>
+      <x:c r="C21" s="240"/>
+      <x:c r="D21" s="240"/>
+      <x:c r="E21" s="240"/>
+      <x:c r="F21" s="240"/>
+      <x:c r="G21" s="240"/>
+      <x:c r="H21" s="240"/>
+      <x:c r="I21" s="241"/>
+    </x:row>
+    <x:row r="22" ht="28" customHeight="1">
+      <x:c r="A22" s="242" t="str">
+        <x:v>현재 구현과 실서비스 경계</x:v>
+      </x:c>
+      <x:c r="B22" s="243"/>
+      <x:c r="C22" s="243"/>
+      <x:c r="D22" s="243"/>
+      <x:c r="E22" s="243"/>
+      <x:c r="F22" s="243"/>
+      <x:c r="G22" s="243"/>
+      <x:c r="H22" s="243"/>
+      <x:c r="I22" s="244"/>
+    </x:row>
+    <x:row r="23" ht="26" customHeight="1">
+      <x:c r="A23" s="245" t="str">
+        <x:v>구분</x:v>
+      </x:c>
+      <x:c r="B23" s="246" t="str">
+        <x:v>현재 동작</x:v>
+      </x:c>
+      <x:c r="C23" s="246" t="str">
+        <x:v>데이터</x:v>
+      </x:c>
+      <x:c r="D23" s="246" t="str">
+        <x:v>사용자에게 표시</x:v>
+      </x:c>
+      <x:c r="E23" s="246" t="str">
+        <x:v>실제 서비스 전환</x:v>
+      </x:c>
+      <x:c r="F23" s="246" t="str">
+        <x:v>우선순위</x:v>
+      </x:c>
+      <x:c r="G23" s="246" t="str">
+        <x:v>대표 문서</x:v>
+      </x:c>
+      <x:c r="H23" s="246" t="str">
+        <x:v>검증</x:v>
+      </x:c>
+      <x:c r="I23" s="247" t="str">
+        <x:v>비고</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="48" customHeight="1">
+      <x:c r="A24" s="218" t="str">
+        <x:v>화면·상호작용</x:v>
+      </x:c>
+      <x:c r="B24" s="218" t="str">
+        <x:v>목적지 선택·5일 편집·필터·추가·이동·삭제·저장</x:v>
+      </x:c>
+      <x:c r="C24" s="218" t="str">
+        <x:v>JSON Fixture + 브라우저 Mock</x:v>
+      </x:c>
+      <x:c r="D24" s="218" t="str">
+        <x:v>Mock/요청/정보/즉시예약 구분</x:v>
+      </x:c>
+      <x:c r="E24" s="218" t="str">
+        <x:v>서버 API와 동일 계약 유지</x:v>
+      </x:c>
+      <x:c r="F24" s="218" t="str">
+        <x:v>완료</x:v>
+      </x:c>
+      <x:c r="G24" s="230" t="str">
+        <x:v>24-product-menu-identity-and-trip-composer-blueprint.md</x:v>
+      </x:c>
+      <x:c r="H24" s="219" t="str">
+        <x:v>브라우저 PASS</x:v>
+      </x:c>
+      <x:c r="I24" s="248" t="str">
+        <x:v>가격·재고 확정 아님</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="48" customHeight="1">
+      <x:c r="A25" s="222" t="str">
+        <x:v>AI</x:v>
+      </x:c>
+      <x:c r="B25" s="222" t="str">
+        <x:v>키워드·기간 인식 후 다카테고리 초안</x:v>
+      </x:c>
+      <x:c r="C25" s="222" t="str">
+        <x:v>Rule-based JSON</x:v>
+      </x:c>
+      <x:c r="D25" s="222" t="str">
+        <x:v>외부 AI 미연결</x:v>
+      </x:c>
+      <x:c r="E25" s="222" t="str">
+        <x:v>LLM Tool Gateway + RAG + 평가</x:v>
+      </x:c>
+      <x:c r="F25" s="222" t="str">
+        <x:v>높음</x:v>
+      </x:c>
+      <x:c r="G25" s="232" t="str">
+        <x:v>16-ai-travel-implementation-report.md</x:v>
+      </x:c>
+      <x:c r="H25" s="223" t="str">
+        <x:v>브라우저 PASS</x:v>
+      </x:c>
+      <x:c r="I25" s="249" t="str">
+        <x:v>근거와 실패 정책 필요</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="48" customHeight="1">
+      <x:c r="A26" s="222" t="str">
+        <x:v>호텔/PMS</x:v>
+      </x:c>
+      <x:c r="B26" s="222" t="str">
+        <x:v>독립 PMS Fixture 조회</x:v>
+      </x:c>
+      <x:c r="C26" s="222" t="str">
+        <x:v>HotelNGo Mock</x:v>
+      </x:c>
+      <x:c r="D26" s="222" t="str">
+        <x:v>마지막 확인·공급 상태</x:v>
+      </x:c>
+      <x:c r="E26" s="222" t="str">
+        <x:v>/api/v1/channel 조회→hold/예약</x:v>
+      </x:c>
+      <x:c r="F26" s="222" t="str">
+        <x:v>최상</x:v>
+      </x:c>
+      <x:c r="G26" s="232" t="str">
+        <x:v>07-pms-integration.md</x:v>
+      </x:c>
+      <x:c r="H26" s="223" t="str">
+        <x:v>계약 테스트 필요</x:v>
+      </x:c>
+      <x:c r="I26" s="249" t="str">
+        <x:v>PMS 회원과 B2C 회원 분리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="48" customHeight="1">
+      <x:c r="A27" s="222" t="str">
+        <x:v>결제·정산</x:v>
+      </x:c>
+      <x:c r="B27" s="222" t="str">
+        <x:v>화면·상태 Mock</x:v>
+      </x:c>
+      <x:c r="C27" s="222" t="str">
+        <x:v>브라우저 상태</x:v>
+      </x:c>
+      <x:c r="D27" s="222" t="str">
+        <x:v>실결제 아님</x:v>
+      </x:c>
+      <x:c r="E27" s="222" t="str">
+        <x:v>PG·원장·환불·정산 API</x:v>
+      </x:c>
+      <x:c r="F27" s="222" t="str">
+        <x:v>최상</x:v>
+      </x:c>
+      <x:c r="G27" s="232" t="str">
+        <x:v>22-end-to-end-process-validation.md</x:v>
+      </x:c>
+      <x:c r="H27" s="223" t="str">
+        <x:v>외부 의존</x:v>
+      </x:c>
+      <x:c r="I27" s="249" t="str">
+        <x:v>금전 거래 없음</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:I1"/>
+    <x:mergeCell ref="A2:I2"/>
+    <x:mergeCell ref="A12:I12"/>
+    <x:mergeCell ref="A22:I22"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="A5:I10">
+    <x:cfRule type="expression" dxfId="72" priority="1">
+      <x:formula>$H5="구현"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="3">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1674cd967deb4258"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bd4f73a548949a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda1215e770bc48ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3076,7 +4401,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="72" t="str">
-        <x:v>총 191개 HTML 제품 화면 · 이 시트의 한 행이 실제 파일 한 개 · 사용자 흐름 단계나 메뉴 항목 수와 구분</x:v>
+        <x:v>총 193개 HTML 제품 화면 · 이 시트의 한 행이 실제 파일 한 개 · 사용자 흐름 단계나 메뉴 항목 수와 구분</x:v>
       </x:c>
       <x:c r="B2" s="72"/>
       <x:c r="C2" s="72"/>
@@ -14469,6 +15794,124 @@
         <x:v>46226</x:v>
       </x:c>
     </x:row>
+    <x:row r="197">
+      <x:c r="A197" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B197" t="str">
+        <x:v>B2C_PUBLIC</x:v>
+      </x:c>
+      <x:c r="C197" t="str">
+        <x:v>호텔</x:v>
+      </x:c>
+      <x:c r="D197" t="str">
+        <x:v>호텔 후기</x:v>
+      </x:c>
+      <x:c r="E197" t="str">
+        <x:v>hotel-reviews.html</x:v>
+      </x:c>
+      <x:c r="F197" t="str">
+        <x:v>호텔 후기 탐색</x:v>
+      </x:c>
+      <x:c r="G197" t="str">
+        <x:v>후기 요약·항목별 평점·여행 유형·객실·정렬 필터·후기 상세 진입</x:v>
+      </x:c>
+      <x:c r="H197" t="str">
+        <x:v>구현</x:v>
+      </x:c>
+      <x:c r="I197" t="str">
+        <x:v>프론트 동작</x:v>
+      </x:c>
+      <x:c r="J197" t="str">
+        <x:v>미연결</x:v>
+      </x:c>
+      <x:c r="K197" t="str">
+        <x:v>예약 확인 후기 요약과 필터·후기 상세 진입을 구현</x:v>
+      </x:c>
+      <x:c r="L197" t="str">
+        <x:v>후기 작성 검증·신고·도움됨 서버 API</x:v>
+      </x:c>
+      <x:c r="M197" t="str">
+        <x:v>9~11, 25</x:v>
+      </x:c>
+      <x:c r="N197" t="str">
+        <x:v>hotel-detail.html → review-detail.html</x:v>
+      </x:c>
+      <x:c r="O197" t="str">
+        <x:v>모바일 전체 메뉴 Drawer · 공통 Toast</x:v>
+      </x:c>
+      <x:c r="P197" t="str">
+        <x:v>http://127.0.0.1:8791/hotel-reviews.html</x:v>
+      </x:c>
+      <x:c r="Q197" t="str">
+        <x:v>https://github.com/giry02/hotelngo/blob/main/hotel-reviews.html</x:v>
+      </x:c>
+      <x:c r="R197" t="str">
+        <x:v>scripts/site-shell.js · scripts/mock-api.js · scripts/platform-flows.js · scripts/auth.js · scripts/main.js · scripts/hotel-detail.js</x:v>
+      </x:c>
+      <x:c r="S197" s="52" t="n">
+        <x:v>46227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" t="n">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B198" t="str">
+        <x:v>B2C_PUBLIC</x:v>
+      </x:c>
+      <x:c r="C198" t="str">
+        <x:v>여행 일정</x:v>
+      </x:c>
+      <x:c r="D198" t="str">
+        <x:v>다일정 여행 편집기</x:v>
+      </x:c>
+      <x:c r="E198" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="F198" t="str">
+        <x:v>4박 5일 여행 전체 구성</x:v>
+      </x:c>
+      <x:c r="G198" t="str">
+        <x:v>목적지·날짜·인원 · 5개 DAY · 숙소·랜드마크·식사·골프·스파·투어·이동 · 충돌·비용·예약방식</x:v>
+      </x:c>
+      <x:c r="H198" t="str">
+        <x:v>구현</x:v>
+      </x:c>
+      <x:c r="I198" t="str">
+        <x:v>Mock 동작</x:v>
+      </x:c>
+      <x:c r="J198" t="str">
+        <x:v>미연결</x:v>
+      </x:c>
+      <x:c r="K198" t="str">
+        <x:v>한 날짜에 여러 업종을 추가·이동·삭제하고 JSON Mock TripDraft로 저장</x:v>
+      </x:c>
+      <x:c r="L198" t="str">
+        <x:v>서버 일정 DB·지도 이동시간·실재고·공동 편집</x:v>
+      </x:c>
+      <x:c r="M198" t="str">
+        <x:v>17, 19~21</x:v>
+      </x:c>
+      <x:c r="N198" t="str">
+        <x:v>discover.html → experiences.html / hotels.html / ai-travel.html → trips.html</x:v>
+      </x:c>
+      <x:c r="O198" t="str">
+        <x:v>목적지 컨텍스트 · DAY 탭 · 카테고리 필터 · 공통 Toast</x:v>
+      </x:c>
+      <x:c r="P198" t="str">
+        <x:v>http://127.0.0.1:8791/trip-planner.html</x:v>
+      </x:c>
+      <x:c r="Q198" t="str">
+        <x:v>https://github.com/giry02/hotelngo/blob/main/trip-planner.html</x:v>
+      </x:c>
+      <x:c r="R198" t="str">
+        <x:v>scripts/site-shell.js · scripts/mock-api.js · scripts/trip-planner.js</x:v>
+      </x:c>
+      <x:c r="S198" s="52" t="n">
+        <x:v>46227</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:S1"/>
@@ -14485,7 +15928,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a510cfd75614523"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R821640e192b34e50"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14511,7 +15954,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="71" t="str">
-        <x:v>사용자 흐름 47단계</x:v>
+        <x:v>사용자 흐름 54단계</x:v>
       </x:c>
       <x:c r="B1" s="71"/>
       <x:c r="C1" s="71"/>
@@ -14528,7 +15971,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="72" t="str">
-        <x:v>총 47개 흐름 단계 · 같은 페이지가 여러 흐름에 다시 등장할 수 있으므로 화면 파일 수와 일치하지 않음</x:v>
+        <x:v>총 54개 흐름 단계 · 같은 페이지가 여러 흐름에 다시 등장할 수 있으므로 화면 파일 수와 일치하지 않음</x:v>
       </x:c>
       <x:c r="B2" s="72"/>
       <x:c r="C2" s="72"/>
@@ -16541,6 +17984,293 @@
       </x:c>
       <x:c r="M52" s="85" t="str">
         <x:v>14~16, 22~24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="str">
+        <x:v>F11</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>B2C_PUBLIC</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>목적지 기반 여행 구성</x:v>
+      </x:c>
+      <x:c r="D53" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E53" t="str">
+        <x:v>discover.html</x:v>
+      </x:c>
+      <x:c r="F53" t="str">
+        <x:v>목적지 미정이면 도시·테마를 발견하고 도시를 선택</x:v>
+      </x:c>
+      <x:c r="G53" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="H53" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="I53" t="str">
+        <x:v>정적+JSON Mock</x:v>
+      </x:c>
+      <x:c r="J53" t="str">
+        <x:v>동작</x:v>
+      </x:c>
+      <x:c r="K53" t="str">
+        <x:v>http://127.0.0.1:8791/discover.html</x:v>
+      </x:c>
+      <x:c r="L53" t="str">
+        <x:v>https://github.com/giry02/hotelngo/blob/main/discover.html</x:v>
+      </x:c>
+      <x:c r="M53" t="str">
+        <x:v>7, 17, 19~21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str">
+        <x:v>F11</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>B2C_PUBLIC</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>목적지 기반 여행 구성</x:v>
+      </x:c>
+      <x:c r="D54" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E54" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="F54" t="str">
+        <x:v>목적지·출귀국일·인원을 확정하고 5개 DAY를 생성</x:v>
+      </x:c>
+      <x:c r="G54" t="str">
+        <x:v>experiences.html / hotels.html</x:v>
+      </x:c>
+      <x:c r="H54" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="I54" t="str">
+        <x:v>trip-planner-catalog JSON</x:v>
+      </x:c>
+      <x:c r="J54" t="str">
+        <x:v>Mock 동작</x:v>
+      </x:c>
+      <x:c r="K54" t="str">
+        <x:v>http://127.0.0.1:8791/trip-planner.html</x:v>
+      </x:c>
+      <x:c r="L54" t="str">
+        <x:v>https://github.com/giry02/hotelngo/blob/main/trip-planner.html</x:v>
+      </x:c>
+      <x:c r="M54" t="str">
+        <x:v>17, 19~21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str">
+        <x:v>F11</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>B2C_PUBLIC</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>목적지 기반 여행 구성</x:v>
+      </x:c>
+      <x:c r="D55" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E55" t="str">
+        <x:v>experiences.html</x:v>
+      </x:c>
+      <x:c r="F55" t="str">
+        <x:v>선택 도시의 랜드마크·식사·골프·스파·투어·이동 후보 탐색</x:v>
+      </x:c>
+      <x:c r="G55" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="H55" t="str">
+        <x:v>목적지</x:v>
+      </x:c>
+      <x:c r="I55" t="str">
+        <x:v>trip-planner-catalog JSON</x:v>
+      </x:c>
+      <x:c r="J55" t="str">
+        <x:v>Mock 동작</x:v>
+      </x:c>
+      <x:c r="K55" t="str">
+        <x:v>http://127.0.0.1:8791/experiences.html?destination=다낭</x:v>
+      </x:c>
+      <x:c r="L55" t="str">
+        <x:v>https://github.com/giry02/hotelngo/blob/main/experiences.html</x:v>
+      </x:c>
+      <x:c r="M55" t="str">
+        <x:v>9, 13, 17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str">
+        <x:v>F11</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>B2C_PUBLIC</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>목적지 기반 여행 구성</x:v>
+      </x:c>
+      <x:c r="D56" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E56" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="F56" t="str">
+        <x:v>항목별 DAY·시간을 선택해 같은 날 여러 업종을 조합</x:v>
+      </x:c>
+      <x:c r="G56" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="H56" t="str">
+        <x:v>목적지·날짜</x:v>
+      </x:c>
+      <x:c r="I56" t="str">
+        <x:v>TripDraft Mock</x:v>
+      </x:c>
+      <x:c r="J56" t="str">
+        <x:v>Mock 동작</x:v>
+      </x:c>
+      <x:c r="K56" t="str">
+        <x:v>http://127.0.0.1:8791/trip-planner.html?destination=다낭&amp;nights=4</x:v>
+      </x:c>
+      <x:c r="L56" t="str">
+        <x:v>https://github.com/giry02/hotelngo/blob/main/trip-planner.html</x:v>
+      </x:c>
+      <x:c r="M56" t="str">
+        <x:v>17, 19~21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="str">
+        <x:v>F11</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>B2C_PUBLIC</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>목적지 기반 여행 구성</x:v>
+      </x:c>
+      <x:c r="D57" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E57" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="F57" t="str">
+        <x:v>시간 충돌·숙소·식사·이동·예상비용·예약방식을 검증</x:v>
+      </x:c>
+      <x:c r="G57" t="str">
+        <x:v>trips.html</x:v>
+      </x:c>
+      <x:c r="H57" t="str">
+        <x:v>일정 항목</x:v>
+      </x:c>
+      <x:c r="I57" t="str">
+        <x:v>TripDraft Mock</x:v>
+      </x:c>
+      <x:c r="J57" t="str">
+        <x:v>Mock 동작</x:v>
+      </x:c>
+      <x:c r="K57" t="str">
+        <x:v>http://127.0.0.1:8791/trip-planner.html?destination=다낭&amp;nights=4</x:v>
+      </x:c>
+      <x:c r="L57" t="str">
+        <x:v>https://github.com/giry02/hotelngo/blob/main/trip-planner.html</x:v>
+      </x:c>
+      <x:c r="M57" t="str">
+        <x:v>17, 19~21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str">
+        <x:v>F11</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>B2C_PUBLIC</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>목적지 기반 여행 구성</x:v>
+      </x:c>
+      <x:c r="D58" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E58" t="str">
+        <x:v>ai-travel.html</x:v>
+      </x:c>
+      <x:c r="F58" t="str">
+        <x:v>자연어 조건으로 동일한 다카테고리 TripDraft 생성</x:v>
+      </x:c>
+      <x:c r="G58" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="H58" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="I58" t="str">
+        <x:v>Rule-based+catalog JSON</x:v>
+      </x:c>
+      <x:c r="J58" t="str">
+        <x:v>Mock 동작</x:v>
+      </x:c>
+      <x:c r="K58" t="str">
+        <x:v>http://127.0.0.1:8791/ai-travel.html</x:v>
+      </x:c>
+      <x:c r="L58" t="str">
+        <x:v>https://github.com/giry02/hotelngo/blob/main/ai-travel.html</x:v>
+      </x:c>
+      <x:c r="M58" t="str">
+        <x:v>19~21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str">
+        <x:v>F11</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>HOTELNGO_B2C</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>목적지 기반 여행 구성</x:v>
+      </x:c>
+      <x:c r="D59" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E59" t="str">
+        <x:v>trips.html</x:v>
+      </x:c>
+      <x:c r="F59" t="str">
+        <x:v>저장한 여행을 다시 열고 예약 준비·공유·지난 여행을 관리</x:v>
+      </x:c>
+      <x:c r="G59" t="str">
+        <x:v>trip-planner.html / trip-booking-plan.html</x:v>
+      </x:c>
+      <x:c r="H59" t="str">
+        <x:v>로그인</x:v>
+      </x:c>
+      <x:c r="I59" t="str">
+        <x:v>Local/Session Mock</x:v>
+      </x:c>
+      <x:c r="J59" t="str">
+        <x:v>부분</x:v>
+      </x:c>
+      <x:c r="K59" t="str">
+        <x:v>http://127.0.0.1:8791/trips.html</x:v>
+      </x:c>
+      <x:c r="L59" t="str">
+        <x:v>https://github.com/giry02/hotelngo/blob/main/trips.html</x:v>
+      </x:c>
+      <x:c r="M59" t="str">
+        <x:v>17~18, 21~22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16559,7 +18289,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc424a1624af442ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d2d89315ed1432b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16600,7 +18330,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="72" t="str">
-        <x:v>현재 메뉴 71개 + 추가 권장 메뉴 20개 · 메뉴 노드와 실제 화면 파일 수는 별도 집계</x:v>
+        <x:v>현재 메뉴 72개 + 추가 권장 메뉴 20개 · 메뉴 노드와 실제 화면 파일 수는 별도 집계</x:v>
       </x:c>
       <x:c r="B2" s="72"/>
       <x:c r="C2" s="72"/>
@@ -16743,7 +18473,7 @@
         <x:v>구현</x:v>
       </x:c>
       <x:c r="H7" s="84" t="str">
-        <x:v>스토리·테마·랜드마크 탐색</x:v>
+        <x:v>목적지 미정 영감 탐색과 도시 선택·도시별 발견</x:v>
       </x:c>
       <x:c r="I7" s="92" t="str">
         <x:v>http://127.0.0.1:8791/discover.html</x:v>
@@ -16755,7 +18485,7 @@
         <x:v>현재</x:v>
       </x:c>
       <x:c r="L7" s="84" t="str">
-        <x:v>공통 셸·사이드바와 화면 연결 완료</x:v>
+        <x:v>선택 도시를 일정·즐길거리·호텔에 전달</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="50" customHeight="1">
@@ -16781,7 +18511,7 @@
         <x:v>구현</x:v>
       </x:c>
       <x:c r="H8" s="84" t="str">
-        <x:v>해외 호텔 검색</x:v>
+        <x:v>선택 목적지·숙박일·인원 기준 호텔·객실·요금 탐색</x:v>
       </x:c>
       <x:c r="I8" s="92" t="str">
         <x:v>http://127.0.0.1:8791/hotels.html</x:v>
@@ -16793,7 +18523,7 @@
         <x:v>현재</x:v>
       </x:c>
       <x:c r="L8" s="84" t="str">
-        <x:v>공통 셸·사이드바와 화면 연결 완료</x:v>
+        <x:v>TripContext와 PMS 공급 계약 연결 대상</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="50" customHeight="1">
@@ -16816,10 +18546,10 @@
         <x:v>전체</x:v>
       </x:c>
       <x:c r="G9" s="111" t="str">
-        <x:v>구현</x:v>
+        <x:v>Mock 동작</x:v>
       </x:c>
       <x:c r="H9" s="84" t="str">
-        <x:v>투어·티켓·현지 경험</x:v>
+        <x:v>목적지 선택 후 랜드마크·식사·골프·스파·투어·이동 탐색</x:v>
       </x:c>
       <x:c r="I9" s="92" t="str">
         <x:v>http://127.0.0.1:8791/experiences.html</x:v>
@@ -16831,7 +18561,7 @@
         <x:v>현재</x:v>
       </x:c>
       <x:c r="L9" s="84" t="str">
-        <x:v>공통 셸·사이드바와 화면 연결 완료</x:v>
+        <x:v>각 후보를 날짜·시간 선택 후 일정에 추가</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="50" customHeight="1">
@@ -16842,22 +18572,22 @@
         <x:v>공개 웹</x:v>
       </x:c>
       <x:c r="C10" s="84" t="str">
-        <x:v>주요 메뉴</x:v>
+        <x:v>즐길거리</x:v>
       </x:c>
       <x:c r="D10" s="84" t="str">
-        <x:v>현지 장소</x:v>
+        <x:v>업체·장소 상세</x:v>
       </x:c>
       <x:c r="E10" s="84" t="str">
-        <x:v>places.html</x:v>
+        <x:v>places.html / place-detail.html</x:v>
       </x:c>
       <x:c r="F10" s="111" t="str">
         <x:v>전체</x:v>
       </x:c>
       <x:c r="G10" s="111" t="str">
-        <x:v>구현</x:v>
+        <x:v>Mock 동작</x:v>
       </x:c>
       <x:c r="H10" s="84" t="str">
-        <x:v>호텔 외 업체·장소 통합 탐색</x:v>
+        <x:v>업체·장소의 실제 공개정보와 예약방식 상세</x:v>
       </x:c>
       <x:c r="I10" s="92" t="str">
         <x:v>http://127.0.0.1:8791/places.html</x:v>
@@ -16869,7 +18599,7 @@
         <x:v>현재</x:v>
       </x:c>
       <x:c r="L10" s="84" t="str">
-        <x:v>공통 셸·사이드바와 화면 연결 완료</x:v>
+        <x:v>상단 중복 메뉴에서 제거하고 즐길거리 내부 데이터로 사용</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="50" customHeight="1">
@@ -16895,7 +18625,7 @@
         <x:v>Mock 동작</x:v>
       </x:c>
       <x:c r="H11" s="84" t="str">
-        <x:v>규칙형 일정 생성·실 AI 미연결</x:v>
+        <x:v>자연어에서 숙소·식사·골프·스파·이동을 포함한 동일 TripDraft 생성</x:v>
       </x:c>
       <x:c r="I11" s="92" t="str">
         <x:v>http://127.0.0.1:8791/ai-travel.html</x:v>
@@ -16907,7 +18637,7 @@
         <x:v>현재</x:v>
       </x:c>
       <x:c r="L11" s="84" t="str">
-        <x:v>공통 셸·사이드바와 화면 연결 완료</x:v>
+        <x:v>실 LLM/RAG 미연결·규칙형 JSON Mock</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="50" customHeight="1">
@@ -16924,7 +18654,7 @@
         <x:v>여행 일정</x:v>
       </x:c>
       <x:c r="E12" s="84" t="str">
-        <x:v>community.html</x:v>
+        <x:v>trip-planner.html</x:v>
       </x:c>
       <x:c r="F12" s="111" t="str">
         <x:v>전체</x:v>
@@ -16933,19 +18663,19 @@
         <x:v>Mock 동작</x:v>
       </x:c>
       <x:c r="H12" s="84" t="str">
-        <x:v>회원 공개 일정 탐색·복사</x:v>
+        <x:v>목적지·날짜·인원과 다카테고리 5일 일정을 직접 편집</x:v>
       </x:c>
       <x:c r="I12" s="92" t="str">
-        <x:v>http://127.0.0.1:8791/community.html</x:v>
+        <x:v>http://127.0.0.1:8791/trip-planner.html</x:v>
       </x:c>
       <x:c r="J12" s="92" t="str">
-        <x:v>https://github.com/giry02/hotelngo/blob/main/community.html</x:v>
+        <x:v>https://github.com/giry02/hotelngo/blob/main/trip-planner.html</x:v>
       </x:c>
       <x:c r="K12" s="84" t="str">
         <x:v>현재</x:v>
       </x:c>
       <x:c r="L12" s="84" t="str">
-        <x:v>공통 셸·사이드바와 화면 연결 완료</x:v>
+        <x:v>HotelNGo 핵심 작업 공간</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="50" customHeight="1">
@@ -20138,6 +21868,44 @@
       </x:c>
       <x:c r="L96" s="85" t="str">
         <x:v>공통 셸·사이드바와 화면 연결 완료</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>B2C_PUBLIC</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>공개 웹</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>여행 발견</x:v>
+      </x:c>
+      <x:c r="D97" t="str">
+        <x:v>다른 여행자의 공개 일정</x:v>
+      </x:c>
+      <x:c r="E97" t="str">
+        <x:v>community.html</x:v>
+      </x:c>
+      <x:c r="F97" t="str">
+        <x:v>전체</x:v>
+      </x:c>
+      <x:c r="G97" t="str">
+        <x:v>Mock 동작</x:v>
+      </x:c>
+      <x:c r="H97" t="str">
+        <x:v>회원·가이드가 공개한 일정 탐색·복사</x:v>
+      </x:c>
+      <x:c r="I97" t="str">
+        <x:v>http://127.0.0.1:8791/community.html</x:v>
+      </x:c>
+      <x:c r="J97" t="str">
+        <x:v>https://github.com/giry02/hotelngo/blob/main/community.html</x:v>
+      </x:c>
+      <x:c r="K97" t="str">
+        <x:v>현재</x:v>
+      </x:c>
+      <x:c r="L97" t="str">
+        <x:v>여행 일정 편집기와 구분되는 발견 콘텐츠</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -20164,7 +21932,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78aa75679c6344a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f4b86eca25f4918"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29288,6 +31056,100 @@
         <x:v>실제 서비스 API와 영속 데이터 저장소</x:v>
       </x:c>
     </x:row>
+    <x:row r="197">
+      <x:c r="A197" t="str">
+        <x:v>C192</x:v>
+      </x:c>
+      <x:c r="B197" t="str">
+        <x:v>B2C_PUBLIC</x:v>
+      </x:c>
+      <x:c r="C197" t="str">
+        <x:v>호텔</x:v>
+      </x:c>
+      <x:c r="D197" t="str">
+        <x:v>호텔 후기</x:v>
+      </x:c>
+      <x:c r="E197" t="str">
+        <x:v>hotel-reviews.html</x:v>
+      </x:c>
+      <x:c r="F197" t="str">
+        <x:v>hotel-detail.html → hotel-reviews.html</x:v>
+      </x:c>
+      <x:c r="G197" t="str">
+        <x:v>현재 화면</x:v>
+      </x:c>
+      <x:c r="H197" t="str">
+        <x:v>구현</x:v>
+      </x:c>
+      <x:c r="I197" t="str">
+        <x:v>프론트 동작</x:v>
+      </x:c>
+      <x:c r="J197" t="str">
+        <x:v>미연결</x:v>
+      </x:c>
+      <x:c r="K197" t="str">
+        <x:v>기존 보완</x:v>
+      </x:c>
+      <x:c r="L197" t="str">
+        <x:v>호텔 후기 탐색과 상세 진입</x:v>
+      </x:c>
+      <x:c r="M197" t="str">
+        <x:v>http://127.0.0.1:8791/hotel-reviews.html</x:v>
+      </x:c>
+      <x:c r="N197" t="str">
+        <x:v>https://github.com/giry02/hotelngo/blob/main/hotel-reviews.html</x:v>
+      </x:c>
+      <x:c r="O197" t="str">
+        <x:v>예약 검증·신고·도움됨 서버 API</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" t="str">
+        <x:v>C193</x:v>
+      </x:c>
+      <x:c r="B198" t="str">
+        <x:v>B2C_PUBLIC</x:v>
+      </x:c>
+      <x:c r="C198" t="str">
+        <x:v>여행 일정</x:v>
+      </x:c>
+      <x:c r="D198" t="str">
+        <x:v>다일정 여행 편집기</x:v>
+      </x:c>
+      <x:c r="E198" t="str">
+        <x:v>trip-planner.html</x:v>
+      </x:c>
+      <x:c r="F198" t="str">
+        <x:v>discover.html / ai-travel.html / experiences.html → trip-planner.html → trips.html</x:v>
+      </x:c>
+      <x:c r="G198" t="str">
+        <x:v>현재 화면</x:v>
+      </x:c>
+      <x:c r="H198" t="str">
+        <x:v>구현</x:v>
+      </x:c>
+      <x:c r="I198" t="str">
+        <x:v>Mock 동작</x:v>
+      </x:c>
+      <x:c r="J198" t="str">
+        <x:v>미연결</x:v>
+      </x:c>
+      <x:c r="K198" t="str">
+        <x:v>신규 핵심</x:v>
+      </x:c>
+      <x:c r="L198" t="str">
+        <x:v>목적지·날짜·인원을 기준으로 숙소·랜드마크·식사·골프·스파·투어·이동을 5일 타임라인에 조합</x:v>
+      </x:c>
+      <x:c r="M198" t="str">
+        <x:v>http://127.0.0.1:8791/trip-planner.html</x:v>
+      </x:c>
+      <x:c r="N198" t="str">
+        <x:v>https://github.com/giry02/hotelngo/blob/main/trip-planner.html</x:v>
+      </x:c>
+      <x:c r="O198" t="str">
+        <x:v>서버 Trip DB·지도 이동시간·실재고·공동 편집</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:O1"/>
@@ -29308,7 +31170,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2686f2630d274ac2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e00200813984f96"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30439,7 +32301,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8247d9a2132466c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7ce2c5312964947"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31686,7 +33548,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58fba1bccf144ea4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8085b79317ce46fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33113,7 +34975,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbab665b8b0114552"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R930ca821fa484765"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33169,7 +35031,9 @@
       <x:c r="L2" s="72"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="73"/>
+      <x:c r="A3" s="73" t="str">
+        <x:v>현재 19개 업무 유스케이스 중 로컬 JSON Mock 18개 통과, Hotel_PMS 실서버 의존 1개입니다.</x:v>
+      </x:c>
       <x:c r="B3" s="73"/>
       <x:c r="C3" s="73"/>
       <x:c r="D3" s="73"/>
@@ -33918,6 +35782,44 @@
       </x:c>
       <x:c r="L23" s="114" t="str">
         <x:v>https://github.com/giry02/hotelngo/blob/main/docs/hotelngo/22-end-to-end-process-validation.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>UC-B2C-08</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>B2C 회원</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>목적지 선택·4박 5일 다일정 여행 조합</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>다낭을 선택하고 숙소·공항 이동·랜드마크·식사·골프·스파·투어를 DAY별로 조합·저장한다.</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>discover.html → trip-planner.html → experiences.html → trip-planner.html → trips.html</x:v>
+      </x:c>
+      <x:c r="F24" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>trip-planner-catalog/TripDraft JSON Mock state</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>LOCAL_PASS</x:v>
+      </x:c>
+      <x:c r="I24" t="str">
+        <x:v>서버 Trip DB·지도 이동시간·실재고·공동 편집</x:v>
+      </x:c>
+      <x:c r="J24" t="str">
+        <x:v>http://127.0.0.1:8791/trip-planner.html?destination=다낭&amp;nights=4</x:v>
+      </x:c>
+      <x:c r="K24" t="str">
+        <x:v>https://github.com/giry02/hotelngo/blob/main/trip-planner.html</x:v>
+      </x:c>
+      <x:c r="L24" t="str">
+        <x:v>docs/hotelngo/24-product-menu-identity-and-trip-composer-blueprint.md</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -33932,7 +35834,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1795856c263c4708"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2fc8f366a5b4eb2"/>
   </x:tableParts>
 </x:worksheet>
 </file>